--- a/backend/data/financials_by_company/1DHER.MI.xlsx
+++ b/backend/data/financials_by_company/1DHER.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB5"/>
+  <dimension ref="A1:BB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,654 +692,712 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-112650000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D2" t="n">
-        <v>901200000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-661300000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-751000000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-882400000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>465400000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>8965400000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>239900000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-225500000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-255000000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>316900000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>96000000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-154350000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-882400000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>11853600000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>-341300000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>14400000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>284245000</v>
+        <v>245865000</v>
       </c>
       <c r="U2" t="n">
-        <v>284245000</v>
+        <v>245865000</v>
       </c>
       <c r="V2" t="n">
-        <v>-3.1</v>
+        <v>-4.57</v>
       </c>
       <c r="W2" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-882400000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-882400000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-882400000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-800000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-881700000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-881700000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>339300000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-542400000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-794200000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>33100000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>30100000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>641300000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-255000000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>34100000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>316900000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>96000000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>441000000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2888200000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>366800000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>404600000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>53100000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>351500000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1149600000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>756400000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>393200000</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>3329200000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>8965400000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>12294800000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>12294800000</v>
-      </c>
+        <v>-4.57</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>14400000</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-239985000</v>
+        <v>-247500000</v>
       </c>
       <c r="C3" t="n">
         <v>0.15</v>
       </c>
       <c r="D3" t="n">
-        <v>-562900000</v>
+        <v>-1262600000</v>
       </c>
       <c r="E3" t="n">
-        <v>-742100000</v>
+        <v>-889100000</v>
       </c>
       <c r="F3" t="n">
-        <v>-1599900000</v>
+        <v>-1650000000</v>
       </c>
       <c r="G3" t="n">
-        <v>-2297500000</v>
+        <v>-3008400000</v>
       </c>
       <c r="H3" t="n">
-        <v>475000000</v>
+        <v>476200000</v>
       </c>
       <c r="I3" t="n">
-        <v>6969000000</v>
+        <v>6345500000</v>
       </c>
       <c r="J3" t="n">
-        <v>-1305000000</v>
+        <v>-2151700000</v>
       </c>
       <c r="K3" t="n">
-        <v>-1803600000</v>
+        <v>-2627900000</v>
       </c>
       <c r="L3" t="n">
-        <v>-237800000</v>
+        <v>-186600000</v>
       </c>
       <c r="M3" t="n">
-        <v>359000000</v>
+        <v>224400000</v>
       </c>
       <c r="N3" t="n">
-        <v>126700000</v>
+        <v>45200000</v>
       </c>
       <c r="O3" t="n">
-        <v>-79785000</v>
+        <v>-845000000</v>
       </c>
       <c r="P3" t="n">
-        <v>-2297500000</v>
+        <v>-3008400000</v>
       </c>
       <c r="Q3" t="n">
-        <v>10124300000</v>
+        <v>9423700000</v>
       </c>
       <c r="R3" t="n">
-        <v>7500000</v>
+        <v>14300000</v>
       </c>
       <c r="S3" t="n">
-        <v>-1656900000</v>
+        <v>-2294600000</v>
       </c>
       <c r="T3" t="n">
-        <v>268213000</v>
+        <v>266766000</v>
       </c>
       <c r="U3" t="n">
-        <v>268213000</v>
+        <v>266766000</v>
       </c>
       <c r="V3" t="n">
-        <v>-8.57</v>
+        <v>-11.28</v>
       </c>
       <c r="W3" t="n">
-        <v>-8.57</v>
+        <v>-11.28</v>
       </c>
       <c r="X3" t="n">
-        <v>-2297500000</v>
+        <v>-3008400000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-2297500000</v>
+        <v>-3008400000</v>
       </c>
       <c r="Z3" t="n">
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2297500000</v>
+        <v>-3008400000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7200000</v>
+        <v>-14900000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2304700000</v>
+        <v>-2993500000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-2304700000</v>
+        <v>-2993500000</v>
       </c>
       <c r="AE3" t="n">
-        <v>142100000</v>
+        <v>141200000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-2162600000</v>
+        <v>-2852300000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1473900000</v>
+        <v>-1483300000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-41300000</v>
+        <v>86500000</v>
       </c>
       <c r="AI3" t="n">
-        <v>30900000</v>
+        <v>38900000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>626500000</v>
+        <v>597000000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-237800000</v>
+        <v>-186600000</v>
       </c>
       <c r="AL3" t="n">
-        <v>5500000</v>
+        <v>7400000</v>
       </c>
       <c r="AM3" t="n">
-        <v>359000000</v>
+        <v>224400000</v>
       </c>
       <c r="AN3" t="n">
-        <v>126700000</v>
+        <v>45200000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-182600000</v>
+        <v>-846400000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3155300000</v>
+        <v>3078200000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>192700000</v>
+        <v>161300000</v>
       </c>
       <c r="AR3" t="n">
-        <v>498600000</v>
+        <v>332800000</v>
       </c>
       <c r="AS3" t="n">
-        <v>55900000</v>
+        <v>51900000</v>
       </c>
       <c r="AT3" t="n">
-        <v>442700000</v>
+        <v>280900000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1101100000</v>
+        <v>1251600000</v>
       </c>
       <c r="AV3" t="n">
-        <v>775800000</v>
+        <v>816700000</v>
       </c>
       <c r="AW3" t="n">
-        <v>325300000</v>
+        <v>434900000</v>
       </c>
       <c r="AX3" t="n">
-        <v>7500000</v>
+        <v>14300000</v>
       </c>
       <c r="AY3" t="n">
-        <v>2972700000</v>
+        <v>2231800000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6969000000</v>
+        <v>6345500000</v>
       </c>
       <c r="BA3" t="n">
-        <v>9941800000</v>
+        <v>8577400000</v>
       </c>
       <c r="BB3" t="n">
-        <v>9941800000</v>
+        <v>8577400000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-247500000</v>
+        <v>-239985000</v>
       </c>
       <c r="C4" t="n">
         <v>0.15</v>
       </c>
       <c r="D4" t="n">
-        <v>-1262600000</v>
+        <v>-562900000</v>
       </c>
       <c r="E4" t="n">
-        <v>-889100000</v>
+        <v>-742100000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1650000000</v>
+        <v>-1599900000</v>
       </c>
       <c r="G4" t="n">
-        <v>-3008400000</v>
+        <v>-2297500000</v>
       </c>
       <c r="H4" t="n">
-        <v>476200000</v>
+        <v>475000000</v>
       </c>
       <c r="I4" t="n">
-        <v>6345500000</v>
+        <v>6969000000</v>
       </c>
       <c r="J4" t="n">
-        <v>-2151700000</v>
+        <v>-1305000000</v>
       </c>
       <c r="K4" t="n">
-        <v>-2627900000</v>
+        <v>-1803600000</v>
       </c>
       <c r="L4" t="n">
-        <v>-186600000</v>
+        <v>-237800000</v>
       </c>
       <c r="M4" t="n">
-        <v>224400000</v>
+        <v>359000000</v>
       </c>
       <c r="N4" t="n">
-        <v>45200000</v>
+        <v>126700000</v>
       </c>
       <c r="O4" t="n">
-        <v>-845000000</v>
+        <v>-79785000</v>
       </c>
       <c r="P4" t="n">
-        <v>-3008400000</v>
+        <v>-2297500000</v>
       </c>
       <c r="Q4" t="n">
-        <v>9423700000</v>
+        <v>10124300000</v>
       </c>
       <c r="R4" t="n">
-        <v>14300000</v>
+        <v>7500000</v>
       </c>
       <c r="S4" t="n">
-        <v>-2294600000</v>
+        <v>-1656900000</v>
       </c>
       <c r="T4" t="n">
-        <v>266766000</v>
+        <v>268213000</v>
       </c>
       <c r="U4" t="n">
-        <v>266766000</v>
+        <v>268213000</v>
       </c>
       <c r="V4" t="n">
-        <v>-11.28</v>
+        <v>-8.57</v>
       </c>
       <c r="W4" t="n">
-        <v>-11.28</v>
+        <v>-8.57</v>
       </c>
       <c r="X4" t="n">
-        <v>-3008400000</v>
+        <v>-2297500000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-3008400000</v>
+        <v>-2297500000</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3008400000</v>
+        <v>-2297500000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-14900000</v>
+        <v>7200000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2993500000</v>
+        <v>-2304700000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2993500000</v>
+        <v>-2304700000</v>
       </c>
       <c r="AE4" t="n">
-        <v>141200000</v>
+        <v>142100000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-2852300000</v>
+        <v>-2162600000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1483300000</v>
+        <v>-1473900000</v>
       </c>
       <c r="AH4" t="n">
-        <v>86500000</v>
+        <v>-41300000</v>
       </c>
       <c r="AI4" t="n">
-        <v>38900000</v>
+        <v>30900000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>597000000</v>
+        <v>626500000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-186600000</v>
+        <v>-237800000</v>
       </c>
       <c r="AL4" t="n">
-        <v>7400000</v>
+        <v>5500000</v>
       </c>
       <c r="AM4" t="n">
-        <v>224400000</v>
+        <v>359000000</v>
       </c>
       <c r="AN4" t="n">
-        <v>45200000</v>
+        <v>126700000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-846400000</v>
+        <v>-182600000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3078200000</v>
+        <v>3155300000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>161300000</v>
+        <v>192700000</v>
       </c>
       <c r="AR4" t="n">
-        <v>332800000</v>
+        <v>498600000</v>
       </c>
       <c r="AS4" t="n">
-        <v>51900000</v>
+        <v>55900000</v>
       </c>
       <c r="AT4" t="n">
-        <v>280900000</v>
+        <v>442700000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1251600000</v>
+        <v>1101100000</v>
       </c>
       <c r="AV4" t="n">
-        <v>816700000</v>
+        <v>775800000</v>
       </c>
       <c r="AW4" t="n">
-        <v>434900000</v>
+        <v>325300000</v>
       </c>
       <c r="AX4" t="n">
-        <v>14300000</v>
+        <v>7500000</v>
       </c>
       <c r="AY4" t="n">
-        <v>2231800000</v>
+        <v>2972700000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6345500000</v>
+        <v>6969000000</v>
       </c>
       <c r="BA4" t="n">
-        <v>8577400000</v>
+        <v>9941800000</v>
       </c>
       <c r="BB4" t="n">
-        <v>8577400000</v>
+        <v>9941800000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>111030000</v>
+        <v>-113760000</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="D5" t="n">
-        <v>-960300000</v>
+        <v>908600000</v>
       </c>
       <c r="E5" t="n">
-        <v>456000000</v>
+        <v>-668700000</v>
       </c>
       <c r="F5" t="n">
-        <v>370100000</v>
+        <v>-758400000</v>
       </c>
       <c r="G5" t="n">
-        <v>-1124300000</v>
+        <v>-882400000</v>
       </c>
       <c r="H5" t="n">
-        <v>350800000</v>
+        <v>465400000</v>
       </c>
       <c r="I5" t="n">
-        <v>4597500000</v>
+        <v>8965400000</v>
       </c>
       <c r="J5" t="n">
-        <v>-504300000</v>
+        <v>239900000</v>
       </c>
       <c r="K5" t="n">
-        <v>-855100000</v>
+        <v>-225500000</v>
       </c>
       <c r="L5" t="n">
-        <v>-137800000</v>
+        <v>-255000000</v>
       </c>
       <c r="M5" t="n">
-        <v>127400000</v>
+        <v>316900000</v>
       </c>
       <c r="N5" t="n">
-        <v>7300000</v>
+        <v>96000000</v>
       </c>
       <c r="O5" t="n">
-        <v>-1297470000</v>
+        <v>-148060000</v>
       </c>
       <c r="P5" t="n">
-        <v>-1124300000</v>
+        <v>-882400000</v>
       </c>
       <c r="Q5" t="n">
-        <v>6948800000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>14400000</v>
-      </c>
+        <v>11846100000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-1079400000</v>
+        <v>-341300000</v>
       </c>
       <c r="T5" t="n">
-        <v>245865000</v>
+        <v>284245000</v>
       </c>
       <c r="U5" t="n">
-        <v>245865000</v>
+        <v>284245000</v>
       </c>
       <c r="V5" t="n">
-        <v>-4.57</v>
+        <v>-3.1</v>
       </c>
       <c r="W5" t="n">
-        <v>-4.57</v>
+        <v>-3.1</v>
       </c>
       <c r="X5" t="n">
-        <v>-1124300000</v>
+        <v>-882400000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-1124300000</v>
+        <v>-882400000</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-1124300000</v>
+        <v>-882400000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-3600000</v>
+        <v>-800000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1120700000</v>
+        <v>-881700000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1120700000</v>
+        <v>-881700000</v>
       </c>
       <c r="AE5" t="n">
-        <v>138200000</v>
+        <v>339300000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-982500000</v>
+        <v>-542400000</v>
       </c>
       <c r="AG5" t="n">
-        <v>31500000</v>
+        <v>-801600000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-656300000</v>
+        <v>40500000</v>
       </c>
       <c r="AI5" t="n">
-        <v>35400000</v>
+        <v>30100000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>503500000</v>
+        <v>641300000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-137800000</v>
+        <v>-255000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>17700000</v>
+        <v>34100000</v>
       </c>
       <c r="AM5" t="n">
-        <v>127400000</v>
+        <v>316900000</v>
       </c>
       <c r="AN5" t="n">
-        <v>7300000</v>
+        <v>96000000</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1093300000</v>
+        <v>448500000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2351300000</v>
+        <v>2880700000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>159000000</v>
+        <v>359300000</v>
       </c>
       <c r="AR5" t="n">
-        <v>229700000</v>
+        <v>404600000</v>
       </c>
       <c r="AS5" t="n">
-        <v>37300000</v>
+        <v>53100000</v>
       </c>
       <c r="AT5" t="n">
-        <v>192400000</v>
+        <v>351500000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1059500000</v>
+        <v>1149600000</v>
       </c>
       <c r="AV5" t="n">
-        <v>759500000</v>
+        <v>756400000</v>
       </c>
       <c r="AW5" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>14400000</v>
-      </c>
+        <v>393200000</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="n">
-        <v>1258000000</v>
+        <v>3329200000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4597500000</v>
+        <v>8965400000</v>
       </c>
       <c r="BA5" t="n">
-        <v>5855600000</v>
+        <v>12294800000</v>
       </c>
       <c r="BB5" t="n">
-        <v>5855600000</v>
+        <v>12294800000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-143535000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1068900000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-697200000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-956900000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-782900000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>457200000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>10626500000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>371700000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-85500000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-287300000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>382100000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>98900000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>290165000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-782900000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>13272800000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>-154100000</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>-782900000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-782900000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-782900000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-84600000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-698200000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-698200000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>230700000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-467600000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-937800000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-12200000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>35900000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>654400000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-287300000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4100000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>382100000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>98900000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>786800000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2646300000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>30800000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>355300000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>41800000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>313500000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1068800000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>723500000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>345300000</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>3433100000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>10626500000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>14059500000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>14059500000</v>
       </c>
     </row>
   </sheetData>
@@ -1353,7 +1411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB5"/>
+  <dimension ref="A1:CB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1755,942 +1813,1032 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>20858</v>
-      </c>
-      <c r="C2" t="n">
-        <v>287365082</v>
-      </c>
-      <c r="D2" t="n">
-        <v>287385940</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1408300000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5667400000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-3401700000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>7809300000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1463600000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-3401700000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>450400000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2592300000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>7659400000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2712500000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>120200000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2592300000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-10208500000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>12513500000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>287400000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>287400000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>9707900000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>5975200000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3400000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>6800000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>28600000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7300000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>30900000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>234700000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>5399600000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>332500000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>5067100000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>256100000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>3732700000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>28700000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>267800000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>117900000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>149900000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>131200000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>852500000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1988100000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>171000000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>561400000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1255700000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>12420400000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>7224100000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>31500000</v>
-      </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
-        <v>22100000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>107200000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>252000000</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="n">
-        <v>252000000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8900000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8900000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>5994000000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>862700000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>5131300000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>770600000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>-860700000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1631300000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>59900000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>559700000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1011700000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>5196300000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>308100000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>-9300000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>25100000</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="n">
+        <v>400000</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
       <c r="BQ2" t="n">
-        <v>225500000</v>
+        <v>4500000</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>19900000</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>174600000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>500400000</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>19800000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>139300000</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>3808700000</v>
-      </c>
-      <c r="BY2" t="inlineStr"/>
-      <c r="BZ2" t="n">
-        <v>3808700000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>2449800000</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>1358900000</v>
-      </c>
+        <v>433000000</v>
+      </c>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="n">
+        <v>12600000</v>
+      </c>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>727863</v>
+        <v>7794307</v>
       </c>
       <c r="C3" t="n">
-        <v>269932634</v>
+        <v>257292148</v>
       </c>
       <c r="D3" t="n">
-        <v>270660497</v>
+        <v>265086455</v>
       </c>
       <c r="E3" t="n">
-        <v>3554700000</v>
+        <v>2835000000</v>
       </c>
       <c r="F3" t="n">
-        <v>5642700000</v>
+        <v>5684600000</v>
       </c>
       <c r="G3" t="n">
-        <v>-4802200000</v>
+        <v>-4165100000</v>
       </c>
       <c r="H3" t="n">
-        <v>6867600000</v>
+        <v>8972500000</v>
       </c>
       <c r="I3" t="n">
-        <v>-109900000</v>
+        <v>1126500000</v>
       </c>
       <c r="J3" t="n">
-        <v>-4802200000</v>
+        <v>-4165100000</v>
       </c>
       <c r="K3" t="n">
-        <v>428600000</v>
+        <v>431800000</v>
       </c>
       <c r="L3" t="n">
-        <v>1653500000</v>
+        <v>3719700000</v>
       </c>
       <c r="M3" t="n">
-        <v>6567500000</v>
+        <v>8959700000</v>
       </c>
       <c r="N3" t="n">
-        <v>1649400000</v>
+        <v>3773700000</v>
       </c>
       <c r="O3" t="n">
-        <v>-4100000</v>
+        <v>54000000</v>
       </c>
       <c r="P3" t="n">
-        <v>1653500000</v>
+        <v>3719700000</v>
       </c>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>-9000000</v>
+      </c>
       <c r="S3" t="n">
-        <v>700000</v>
+        <v>7800000</v>
       </c>
       <c r="T3" t="n">
-        <v>-8878200000</v>
+        <v>-6300400000</v>
       </c>
       <c r="U3" t="n">
-        <v>10261700000</v>
+        <v>9762800000</v>
       </c>
       <c r="V3" t="n">
-        <v>270700000</v>
+        <v>265100000</v>
       </c>
       <c r="W3" t="n">
-        <v>270700000</v>
+        <v>265100000</v>
       </c>
       <c r="X3" t="n">
-        <v>8838400000</v>
+        <v>9086500000</v>
       </c>
       <c r="Y3" t="n">
-        <v>5894000000</v>
+        <v>6684200000</v>
       </c>
       <c r="Z3" t="n">
-        <v>3600000</v>
+        <v>4600000</v>
       </c>
       <c r="AA3" t="n">
-        <v>20200000</v>
+        <v>307100000</v>
       </c>
       <c r="AB3" t="n">
-        <v>21200000</v>
+        <v>20900000</v>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>32400000</v>
+        <v>36100000</v>
       </c>
       <c r="AE3" t="n">
-        <v>262100000</v>
+        <v>288400000</v>
       </c>
       <c r="AF3" t="n">
-        <v>5236900000</v>
+        <v>5556700000</v>
       </c>
       <c r="AG3" t="n">
-        <v>322900000</v>
+        <v>316700000</v>
       </c>
       <c r="AH3" t="n">
-        <v>4914000000</v>
+        <v>5240000000</v>
       </c>
       <c r="AI3" t="n">
-        <v>298300000</v>
+        <v>404500000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2944400000</v>
+        <v>2402300000</v>
       </c>
       <c r="AK3" t="n">
-        <v>29100000</v>
+        <v>29400000</v>
       </c>
       <c r="AL3" t="n">
-        <v>405800000</v>
+        <v>127900000</v>
       </c>
       <c r="AM3" t="n">
-        <v>105700000</v>
+        <v>115100000</v>
       </c>
       <c r="AN3" t="n">
-        <v>300100000</v>
+        <v>12800000</v>
       </c>
       <c r="AO3" t="n">
-        <v>129300000</v>
+        <v>144300000</v>
       </c>
       <c r="AP3" t="n">
-        <v>311000000</v>
+        <v>149700000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1623700000</v>
+        <v>1586100000</v>
       </c>
       <c r="AR3" t="n">
-        <v>168100000</v>
+        <v>273800000</v>
       </c>
       <c r="AS3" t="n">
-        <v>393800000</v>
+        <v>339400000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1061800000</v>
+        <v>972900000</v>
       </c>
       <c r="AU3" t="n">
-        <v>10487800000</v>
+        <v>12860200000</v>
       </c>
       <c r="AV3" t="n">
-        <v>7653300000</v>
+        <v>9331400000</v>
       </c>
       <c r="AW3" t="n">
-        <v>26300000</v>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+        <v>38500000</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>32600000</v>
+      </c>
       <c r="AY3" t="n">
-        <v>8800000</v>
+        <v>4600000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17900000</v>
+        <v>30700000</v>
       </c>
       <c r="BA3" t="n">
-        <v>352400000</v>
+        <v>588600000</v>
       </c>
       <c r="BB3" t="n">
-        <v>408300000</v>
+        <v>588600000</v>
       </c>
       <c r="BC3" t="n">
-        <v>352400000</v>
+        <v>509500000</v>
       </c>
       <c r="BD3" t="n">
-        <v>7600000</v>
+        <v>9900000</v>
       </c>
       <c r="BE3" t="n">
-        <v>7600000</v>
+        <v>9900000</v>
       </c>
       <c r="BF3" t="n">
-        <v>6455700000</v>
+        <v>7884800000</v>
       </c>
       <c r="BG3" t="n">
-        <v>970200000</v>
+        <v>1255500000</v>
       </c>
       <c r="BH3" t="n">
-        <v>5485500000</v>
+        <v>6629300000</v>
       </c>
       <c r="BI3" t="n">
-        <v>746600000</v>
+        <v>805000000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-687100000</v>
+        <v>-557400000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1433700000</v>
+        <v>1362400000</v>
       </c>
       <c r="BL3" t="n">
-        <v>44200000</v>
+        <v>37800000</v>
       </c>
       <c r="BM3" t="n">
-        <v>501700000</v>
+        <v>504100000</v>
       </c>
       <c r="BN3" t="n">
-        <v>887800000</v>
+        <v>820500000</v>
       </c>
       <c r="BO3" t="n">
-        <v>2834500000</v>
+        <v>3528800000</v>
       </c>
       <c r="BP3" t="n">
-        <v>255200000</v>
-      </c>
-      <c r="BQ3" t="inlineStr"/>
+        <v>230200000</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>0</v>
+      </c>
       <c r="BR3" t="n">
-        <v>49700000</v>
+        <v>62800000</v>
       </c>
       <c r="BS3" t="n">
-        <v>25400000</v>
+        <v>20400000</v>
       </c>
       <c r="BT3" t="n">
-        <v>143500000</v>
+        <v>141300000</v>
       </c>
       <c r="BU3" t="n">
-        <v>552900000</v>
+        <v>463800000</v>
       </c>
       <c r="BV3" t="n">
-        <v>9900000</v>
+        <v>18400000</v>
       </c>
       <c r="BW3" t="n">
-        <v>133600000</v>
+        <v>122100000</v>
       </c>
       <c r="BX3" t="n">
-        <v>1664300000</v>
+        <v>2469800000</v>
       </c>
       <c r="BY3" t="n">
-        <v>4900000</v>
+        <v>52000000</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1659400000</v>
+        <v>2417800000</v>
       </c>
       <c r="CA3" t="n">
-        <v>558800000</v>
+        <v>814800000</v>
       </c>
       <c r="CB3" t="n">
-        <v>1100500000</v>
+        <v>1603000000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>7794307</v>
+        <v>727863</v>
       </c>
       <c r="C4" t="n">
-        <v>257292148</v>
+        <v>269932634</v>
       </c>
       <c r="D4" t="n">
-        <v>265086455</v>
+        <v>270660497</v>
       </c>
       <c r="E4" t="n">
-        <v>2835000000</v>
+        <v>3554700000</v>
       </c>
       <c r="F4" t="n">
-        <v>5684600000</v>
+        <v>5642700000</v>
       </c>
       <c r="G4" t="n">
-        <v>-4165100000</v>
+        <v>-4802200000</v>
       </c>
       <c r="H4" t="n">
-        <v>8972500000</v>
+        <v>6867600000</v>
       </c>
       <c r="I4" t="n">
-        <v>1126500000</v>
+        <v>-109900000</v>
       </c>
       <c r="J4" t="n">
-        <v>-4165100000</v>
+        <v>-4802200000</v>
       </c>
       <c r="K4" t="n">
-        <v>431800000</v>
+        <v>428600000</v>
       </c>
       <c r="L4" t="n">
-        <v>3719700000</v>
+        <v>1653500000</v>
       </c>
       <c r="M4" t="n">
-        <v>8959700000</v>
+        <v>6567500000</v>
       </c>
       <c r="N4" t="n">
-        <v>3773700000</v>
+        <v>1649400000</v>
       </c>
       <c r="O4" t="n">
-        <v>54000000</v>
+        <v>-4100000</v>
       </c>
       <c r="P4" t="n">
-        <v>3719700000</v>
+        <v>1653500000</v>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
-        <v>-9000000</v>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>7800000</v>
+        <v>700000</v>
       </c>
       <c r="T4" t="n">
-        <v>-6300400000</v>
+        <v>-8878200000</v>
       </c>
       <c r="U4" t="n">
-        <v>9762800000</v>
+        <v>10261700000</v>
       </c>
       <c r="V4" t="n">
-        <v>265100000</v>
+        <v>270700000</v>
       </c>
       <c r="W4" t="n">
-        <v>265100000</v>
+        <v>270700000</v>
       </c>
       <c r="X4" t="n">
-        <v>9086500000</v>
+        <v>8838400000</v>
       </c>
       <c r="Y4" t="n">
-        <v>6684200000</v>
+        <v>5894000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>4600000</v>
+        <v>3600000</v>
       </c>
       <c r="AA4" t="n">
-        <v>307100000</v>
+        <v>20200000</v>
       </c>
       <c r="AB4" t="n">
-        <v>20900000</v>
+        <v>21200000</v>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>36100000</v>
+        <v>32400000</v>
       </c>
       <c r="AE4" t="n">
-        <v>288400000</v>
+        <v>262100000</v>
       </c>
       <c r="AF4" t="n">
-        <v>5556700000</v>
+        <v>5236900000</v>
       </c>
       <c r="AG4" t="n">
-        <v>316700000</v>
+        <v>322900000</v>
       </c>
       <c r="AH4" t="n">
-        <v>5240000000</v>
+        <v>4914000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>404500000</v>
+        <v>298300000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2402300000</v>
+        <v>2944400000</v>
       </c>
       <c r="AK4" t="n">
-        <v>29400000</v>
+        <v>29100000</v>
       </c>
       <c r="AL4" t="n">
-        <v>127900000</v>
+        <v>405800000</v>
       </c>
       <c r="AM4" t="n">
-        <v>115100000</v>
+        <v>105700000</v>
       </c>
       <c r="AN4" t="n">
-        <v>12800000</v>
+        <v>300100000</v>
       </c>
       <c r="AO4" t="n">
-        <v>144300000</v>
+        <v>129300000</v>
       </c>
       <c r="AP4" t="n">
-        <v>149700000</v>
+        <v>311000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1586100000</v>
+        <v>1623700000</v>
       </c>
       <c r="AR4" t="n">
-        <v>273800000</v>
+        <v>168100000</v>
       </c>
       <c r="AS4" t="n">
-        <v>339400000</v>
+        <v>393800000</v>
       </c>
       <c r="AT4" t="n">
-        <v>972900000</v>
+        <v>1061800000</v>
       </c>
       <c r="AU4" t="n">
-        <v>12860200000</v>
+        <v>10487800000</v>
       </c>
       <c r="AV4" t="n">
-        <v>9331400000</v>
+        <v>7653300000</v>
       </c>
       <c r="AW4" t="n">
-        <v>38500000</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>32600000</v>
-      </c>
+        <v>26300000</v>
+      </c>
+      <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="n">
-        <v>4600000</v>
+        <v>8800000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>30700000</v>
+        <v>17900000</v>
       </c>
       <c r="BA4" t="n">
-        <v>588600000</v>
+        <v>352400000</v>
       </c>
       <c r="BB4" t="n">
-        <v>588600000</v>
+        <v>408300000</v>
       </c>
       <c r="BC4" t="n">
-        <v>509500000</v>
+        <v>352400000</v>
       </c>
       <c r="BD4" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>6455700000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>970200000</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>5485500000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>746600000</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>-687100000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1433700000</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>44200000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>501700000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>887800000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>2834500000</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>255200000</v>
+      </c>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="n">
+        <v>49700000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>25400000</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>143500000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>552900000</v>
+      </c>
+      <c r="BV4" t="n">
         <v>9900000</v>
       </c>
-      <c r="BE4" t="n">
-        <v>9900000</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>7884800000</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1255500000</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>6629300000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>805000000</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>-557400000</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1362400000</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>37800000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>504100000</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>820500000</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>3528800000</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>230200000</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>62800000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>20400000</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>141300000</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>463800000</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>18400000</v>
-      </c>
       <c r="BW4" t="n">
-        <v>122100000</v>
+        <v>133600000</v>
       </c>
       <c r="BX4" t="n">
-        <v>2469800000</v>
+        <v>1664300000</v>
       </c>
       <c r="BY4" t="n">
-        <v>52000000</v>
+        <v>4900000</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2417800000</v>
+        <v>1659400000</v>
       </c>
       <c r="CA4" t="n">
-        <v>814800000</v>
+        <v>558800000</v>
       </c>
       <c r="CB4" t="n">
-        <v>1603000000</v>
+        <v>1100500000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>7800095</v>
+        <v>20858</v>
       </c>
       <c r="C5" t="n">
-        <v>243182444</v>
+        <v>287365082</v>
       </c>
       <c r="D5" t="n">
-        <v>250982539</v>
+        <v>287385940</v>
       </c>
       <c r="E5" t="n">
-        <v>1732800000</v>
+        <v>1408300000</v>
       </c>
       <c r="F5" t="n">
-        <v>4535700000</v>
+        <v>5667400000</v>
       </c>
       <c r="G5" t="n">
-        <v>-1567500000</v>
+        <v>-3403200000</v>
       </c>
       <c r="H5" t="n">
-        <v>9607300000</v>
+        <v>7809300000</v>
       </c>
       <c r="I5" t="n">
-        <v>1840200000</v>
+        <v>1463600000</v>
       </c>
       <c r="J5" t="n">
-        <v>-1567500000</v>
+        <v>-3403200000</v>
       </c>
       <c r="K5" t="n">
-        <v>356200000</v>
+        <v>450400000</v>
       </c>
       <c r="L5" t="n">
-        <v>5427800000</v>
+        <v>2592300000</v>
       </c>
       <c r="M5" t="n">
-        <v>9587400000</v>
+        <v>7659400000</v>
       </c>
       <c r="N5" t="n">
-        <v>5443800000</v>
+        <v>2712500000</v>
       </c>
       <c r="O5" t="n">
-        <v>16000000</v>
+        <v>120200000</v>
       </c>
       <c r="P5" t="n">
-        <v>5427800000</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
-        <v>-9300000</v>
-      </c>
+        <v>2592300000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>7800000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-3323600000</v>
+        <v>-10208500000</v>
       </c>
       <c r="U5" t="n">
-        <v>8901900000</v>
+        <v>12513500000</v>
       </c>
       <c r="V5" t="n">
-        <v>251000000</v>
+        <v>287400000</v>
       </c>
       <c r="W5" t="n">
-        <v>251000000</v>
+        <v>287400000</v>
       </c>
       <c r="X5" t="n">
-        <v>7212700000</v>
+        <v>9707900000</v>
       </c>
       <c r="Y5" t="n">
-        <v>5458100000</v>
+        <v>5975200000</v>
       </c>
       <c r="Z5" t="n">
-        <v>2100000</v>
+        <v>3400000</v>
       </c>
       <c r="AA5" t="n">
-        <v>653100000</v>
+        <v>6800000</v>
       </c>
       <c r="AB5" t="n">
-        <v>32200000</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>28600000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7300000</v>
+      </c>
       <c r="AD5" t="n">
-        <v>35000000</v>
+        <v>30900000</v>
       </c>
       <c r="AE5" t="n">
-        <v>266700000</v>
+        <v>234700000</v>
       </c>
       <c r="AF5" t="n">
-        <v>4422800000</v>
+        <v>5399600000</v>
       </c>
       <c r="AG5" t="n">
-        <v>263200000</v>
+        <v>332500000</v>
       </c>
       <c r="AH5" t="n">
-        <v>4159600000</v>
+        <v>5067100000</v>
       </c>
       <c r="AI5" t="n">
-        <v>26900000</v>
+        <v>256100000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1754600000</v>
+        <v>3732700000</v>
       </c>
       <c r="AK5" t="n">
-        <v>25900000</v>
+        <v>29700000</v>
       </c>
       <c r="AL5" t="n">
-        <v>112900000</v>
+        <v>267800000</v>
       </c>
       <c r="AM5" t="n">
-        <v>93000000</v>
+        <v>117900000</v>
       </c>
       <c r="AN5" t="n">
+        <v>149900000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>130200000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>852500000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1988100000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>171000000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>561400000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1255700000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>12420400000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>7224100000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>22100000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>107200000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>252000000</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="n">
+        <v>252000000</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5995500000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>862800000</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>5132700000</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>770600000</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-860700000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1631300000</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>59900000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>559700000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1011700000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>5196300000</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>308100000</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>225500000</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
         <v>19900000</v>
       </c>
-      <c r="AO5" t="n">
-        <v>98000000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>118600000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1099500000</v>
-      </c>
-      <c r="AR5" t="n">
+      <c r="BT5" t="n">
+        <v>174600000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>500400000</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>19800000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>139300000</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>3808700000</v>
+      </c>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="n">
+        <v>3808700000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>2449800000</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>1358900000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>20701</v>
+      </c>
+      <c r="C6" t="n">
+        <v>298227538</v>
+      </c>
+      <c r="D6" t="n">
+        <v>298248239</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2075000000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4625500000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-3530500000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5827300000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-133900000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-3530500000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>437800000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1639600000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5666500000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1793800000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>154200000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1639600000</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-11373800000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>12715200000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>298200000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>298200000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>8416200000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4989600000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>33800000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>30700000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>10300000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>163300000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4337800000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>310900000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>4026900000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>396900000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>3426600000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>48200000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>287700000</v>
+      </c>
+      <c r="AM6" t="n">
         <v>126900000</v>
       </c>
-      <c r="AS5" t="n">
-        <v>234200000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>738400000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>12656500000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9061800000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>7300000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>25100000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>5200000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1100400000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>400000</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1100000000</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>241300000</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>241300000</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>6995300000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1100500000</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>5894800000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>681100000</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>-329000000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1010100000</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>25300000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>375400000</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>609400000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>3594800000</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>180000000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>433000000</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>23200000</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>79500000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>335200000</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>14100000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>66000000</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>2459300000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>12600000</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>2446700000</v>
-      </c>
-      <c r="CA5" t="inlineStr"/>
-      <c r="CB5" t="n">
-        <v>2446700000</v>
+      <c r="AN6" t="n">
+        <v>160800000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>174000000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>457700000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1964800000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>153100000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>504800000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1306900000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>10210000000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>6917300000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>550700000</v>
+      </c>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>53100000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>86000000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>209800000</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
+        <v>209800000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>9800000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>9800000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5170100000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>745800000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>4424300000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>801500000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-902200000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1703700000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>35300000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>539100000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1129300000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3292700000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>338500000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>600000</v>
+      </c>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="n">
+        <v>15200000</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>190600000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>471300000</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>32600000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>131200000</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>2112700000</v>
+      </c>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="n">
+        <v>2112700000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>855300000</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>1257400000</v>
       </c>
     </row>
   </sheetData>
@@ -2704,7 +2852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA5"/>
+  <dimension ref="A1:BA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2971,592 +3119,665 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>358800000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
-        <v>799300000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2138800000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-279500000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3808700000</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>1659400000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-9100000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2158400000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1579600000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-954900000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-254900000</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
-        <v>2138800000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2138800000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>799300000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>799300000</v>
-      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>799300000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-59500000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="n">
-        <v>58700000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>204100000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>204100000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
-        <v>-46600000</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>-46600000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-140400000</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>-901600000</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>660100000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-140400000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-130800000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>8300000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-139100000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>638300000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-292900000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>630900000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>44900000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>276400000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-193000000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>58400000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-19800000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>171100000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>339300000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>465400000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>465400000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>-1200000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>-881700000</v>
-      </c>
+        <v>200000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>81000000</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-280200000</v>
+        <v>-941600000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1002200000</v>
+        <v>-260100000</v>
       </c>
       <c r="D3" t="n">
-        <v>1000800000</v>
+        <v>1066800000</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3600000</v>
       </c>
       <c r="F3" t="n">
-        <v>-260700000</v>
+        <v>-252800000</v>
       </c>
       <c r="G3" t="n">
-        <v>1659400000</v>
+        <v>2417800000</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>2417800000</v>
+        <v>2448300000</v>
       </c>
       <c r="J3" t="n">
-        <v>-103800000</v>
+        <v>8600000</v>
       </c>
       <c r="K3" t="n">
-        <v>-654600000</v>
+        <v>-39100000</v>
       </c>
       <c r="L3" t="n">
-        <v>-377300000</v>
+        <v>717600000</v>
       </c>
       <c r="M3" t="n">
-        <v>-1044600000</v>
+        <v>-100000</v>
       </c>
       <c r="N3" t="n">
-        <v>-173400000</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-3300000</v>
-      </c>
+        <v>-92600000</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>806700000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>806700000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-260100000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1066800000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-67900000</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>25800000</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1000800000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1000800000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-1002200000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1000800000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-257800000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>50200000</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>63800000</v>
+        <v>216200000</v>
       </c>
       <c r="AA3" t="n">
-        <v>63800000</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+        <v>216200000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-26900000</v>
+      </c>
       <c r="AC3" t="n">
-        <v>-102400000</v>
+        <v>-57600000</v>
       </c>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>-102400000</v>
+        <v>-57600000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-112300000</v>
+        <v>-71400000</v>
       </c>
       <c r="AG3" t="n">
-        <v>700000</v>
+        <v>1300000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-113000000</v>
+        <v>-72700000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-147700000</v>
+        <v>-168100000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>12000000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-147700000</v>
+        <v>-180100000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-19500000</v>
+        <v>-688800000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-198100000</v>
+        <v>-68100000</v>
       </c>
       <c r="AN3" t="n">
-        <v>18100000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>145000000</v>
-      </c>
+        <v>183100000</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>105500000</v>
+        <v>250500000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-165000000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-109400000</v>
-      </c>
+        <v>-171000000</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>514200000</v>
+        <v>470500000</v>
       </c>
       <c r="AT3" t="n">
-        <v>247400000</v>
+        <v>325900000</v>
       </c>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>142100000</v>
+        <v>141200000</v>
       </c>
       <c r="AW3" t="n">
-        <v>475000000</v>
+        <v>476200000</v>
       </c>
       <c r="AX3" t="n">
-        <v>475000000</v>
+        <v>476200000</v>
       </c>
       <c r="AY3" t="n">
-        <v>4200000</v>
+        <v>16500000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11700000</v>
+        <v>-300000</v>
       </c>
       <c r="BA3" t="n">
-        <v>-2304700000</v>
+        <v>-2993500000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-941600000</v>
+        <v>-280200000</v>
       </c>
       <c r="C4" t="n">
-        <v>-260100000</v>
+        <v>-1002200000</v>
       </c>
       <c r="D4" t="n">
-        <v>1066800000</v>
+        <v>1000800000</v>
       </c>
       <c r="E4" t="n">
-        <v>3600000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-252800000</v>
+        <v>-260700000</v>
       </c>
       <c r="G4" t="n">
-        <v>2417800000</v>
+        <v>1659400000</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>2448300000</v>
+        <v>2417800000</v>
       </c>
       <c r="J4" t="n">
-        <v>8600000</v>
+        <v>-103800000</v>
       </c>
       <c r="K4" t="n">
-        <v>-39100000</v>
+        <v>-654600000</v>
       </c>
       <c r="L4" t="n">
-        <v>717600000</v>
+        <v>-377300000</v>
       </c>
       <c r="M4" t="n">
+        <v>-1044600000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-173400000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-3300000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1000800000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1000800000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-1002200000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1000800000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-257800000</v>
+      </c>
+      <c r="W4" t="n">
         <v>-100000</v>
       </c>
-      <c r="N4" t="n">
-        <v>-92600000</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>806700000</v>
-      </c>
-      <c r="S4" t="n">
-        <v>806700000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-260100000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1066800000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>-67900000</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>25800000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
+        <v>50200000</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>216200000</v>
+        <v>63800000</v>
       </c>
       <c r="AA4" t="n">
-        <v>216200000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-26900000</v>
-      </c>
+        <v>63800000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>-57600000</v>
+        <v>-102400000</v>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>-57600000</v>
+        <v>-102400000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-71400000</v>
+        <v>-112300000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1300000</v>
+        <v>700000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-72700000</v>
+        <v>-113000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-168100000</v>
+        <v>-147700000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12000000</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>-180100000</v>
+        <v>-147700000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-688800000</v>
+        <v>-19500000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-68100000</v>
+        <v>-198100000</v>
       </c>
       <c r="AN4" t="n">
-        <v>183100000</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
+        <v>18100000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>145000000</v>
+      </c>
       <c r="AP4" t="n">
-        <v>250500000</v>
+        <v>105500000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-171000000</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
+        <v>-165000000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-109400000</v>
+      </c>
       <c r="AS4" t="n">
-        <v>470500000</v>
+        <v>514200000</v>
       </c>
       <c r="AT4" t="n">
-        <v>325900000</v>
+        <v>247400000</v>
       </c>
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>141200000</v>
+        <v>142100000</v>
       </c>
       <c r="AW4" t="n">
-        <v>476200000</v>
+        <v>475000000</v>
       </c>
       <c r="AX4" t="n">
-        <v>476200000</v>
+        <v>475000000</v>
       </c>
       <c r="AY4" t="n">
-        <v>16500000</v>
+        <v>4200000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-300000</v>
+        <v>11700000</v>
       </c>
       <c r="BA4" t="n">
-        <v>-2993500000</v>
+        <v>-2304700000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1222500000</v>
+        <v>358800000</v>
       </c>
       <c r="C5" t="n">
-        <v>-152300000</v>
+        <v>-875200000</v>
       </c>
       <c r="D5" t="n">
-        <v>1245400000</v>
+        <v>799300000</v>
       </c>
       <c r="E5" t="n">
-        <v>1252900000</v>
+        <v>2138800000</v>
       </c>
       <c r="F5" t="n">
-        <v>-321100000</v>
+        <v>-279500000</v>
       </c>
       <c r="G5" t="n">
-        <v>2448300000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>100000</v>
-      </c>
+        <v>3808700000</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>2977200000</v>
+        <v>1659400000</v>
       </c>
       <c r="J5" t="n">
-        <v>19100000</v>
+        <v>-9100000</v>
       </c>
       <c r="K5" t="n">
-        <v>-548100000</v>
+        <v>2158400000</v>
       </c>
       <c r="L5" t="n">
-        <v>2299300000</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>1579600000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-79700000</v>
+      </c>
       <c r="N5" t="n">
-        <v>-46700000</v>
+        <v>-254900000</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1252900000</v>
+        <v>2138800000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1252900000</v>
+        <v>2138800000</v>
       </c>
       <c r="R5" t="n">
-        <v>1093100000</v>
+        <v>-75900000</v>
       </c>
       <c r="S5" t="n">
-        <v>1093100000</v>
+        <v>-75900000</v>
       </c>
       <c r="T5" t="n">
-        <v>-152300000</v>
+        <v>-875200000</v>
       </c>
       <c r="U5" t="n">
-        <v>1245400000</v>
+        <v>799300000</v>
       </c>
       <c r="V5" t="n">
-        <v>-1946000000</v>
-      </c>
-      <c r="W5" t="n">
+        <v>-59500000</v>
+      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>58700000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>204100000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>204100000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="n">
+        <v>-46600000</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>-46600000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>-140400000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-140400000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-130800000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>8300000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-139100000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>638300000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-292900000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>630900000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>44900000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>276400000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-193000000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>58400000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-19800000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>171100000</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="n">
+        <v>339300000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>465400000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>465400000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>-1200000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-881700000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-246300000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-891500000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1556600000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-325800000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2112700000</v>
+      </c>
+      <c r="H6" t="n">
         <v>-100000</v>
       </c>
-      <c r="X5" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="Y5" t="n">
+      <c r="I6" t="n">
+        <v>3808700000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-156100000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1539800000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1376500000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-1630700000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-246500000</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" t="n">
-        <v>-901600000</v>
-      </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="n">
-        <v>-901600000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-699600000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>660100000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>-1359700000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-53800000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>200000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-54000000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>-267100000</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="n">
-        <v>-267100000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>-901400000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-66100000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>117000000</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="n">
-        <v>395100000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-359100000</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>-39900000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>303100000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>81000000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>138200000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>350800000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>350800000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>-18800000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>-652500000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>-1120700000</v>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>665100000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>665100000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-891500000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1556600000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-242800000</v>
+      </c>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>77700000</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>44300000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>44300000</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>-35500000</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>-35500000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-154800000</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>-154800000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-164800000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-171000000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>79500000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-272600000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-459900000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>97900000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>255500000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-547700000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>313400000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>224100000</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>230700000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>457200000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>457200000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>-800000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-2100000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-698200000</v>
       </c>
     </row>
   </sheetData>
@@ -4086,202 +4307,202 @@
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EM1" t="inlineStr">
@@ -4301,10 +4522,8 @@
           <t>Berlin</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>10117</t>
-        </is>
+      <c r="C2" t="n">
+        <v>10117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4380,7 +4599,7 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="V2" t="n">
         <v>1767139200</v>
@@ -4397,67 +4616,67 @@
         <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>37.77</v>
+        <v>37.23</v>
       </c>
       <c r="AA2" t="n">
-        <v>38.16</v>
+        <v>36.76</v>
       </c>
       <c r="AB2" t="n">
-        <v>38.16</v>
+        <v>36.72</v>
       </c>
       <c r="AC2" t="n">
-        <v>38.16</v>
+        <v>36.76</v>
       </c>
       <c r="AD2" t="n">
-        <v>37.77</v>
+        <v>37.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>38.16</v>
+        <v>36.76</v>
       </c>
       <c r="AF2" t="n">
-        <v>38.16</v>
+        <v>36.72</v>
       </c>
       <c r="AG2" t="n">
-        <v>38.16</v>
+        <v>36.76</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.69</v>
+        <v>1.855</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="AK2" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="AL2" t="n">
-        <v>1415</v>
+        <v>1193</v>
       </c>
       <c r="AM2" t="n">
-        <v>1206</v>
+        <v>82</v>
       </c>
       <c r="AN2" t="n">
-        <v>1206</v>
+        <v>82</v>
       </c>
       <c r="AO2" t="n">
-        <v>38.13</v>
+        <v>36.61</v>
       </c>
       <c r="AP2" t="n">
-        <v>38.28</v>
+        <v>36.87</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11609292800</v>
+        <v>11165817856</v>
       </c>
       <c r="AR2" t="n">
-        <v>11442230179</v>
+        <v>11314655539</v>
       </c>
       <c r="AS2" t="n">
         <v>15.05</v>
       </c>
       <c r="AT2" t="n">
-        <v>39.1</v>
+        <v>39.69</v>
       </c>
       <c r="AU2" t="n">
         <v>41.58</v>
@@ -4466,13 +4685,13 @@
         <v>15.05</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.82572</v>
+        <v>0.7941775</v>
       </c>
       <c r="AX2" t="n">
-        <v>22.7624</v>
+        <v>28.4194</v>
       </c>
       <c r="AY2" t="n">
-        <v>22.1932</v>
+        <v>23.0947</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -4489,22 +4708,22 @@
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>14065256448</v>
+        <v>14104026112</v>
       </c>
       <c r="BE2" t="n">
         <v>-0.05568</v>
       </c>
       <c r="BF2" t="n">
-        <v>201768823</v>
+        <v>203519419</v>
       </c>
       <c r="BG2" t="n">
         <v>303749142</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.41818002</v>
+        <v>0.41813</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.56926996</v>
+        <v>0.62356997</v>
       </c>
       <c r="BJ2" t="n">
         <v>303749142</v>
@@ -4513,7 +4732,7 @@
         <v>5.498</v>
       </c>
       <c r="BL2" t="n">
-        <v>6.9516187</v>
+        <v>6.686067</v>
       </c>
       <c r="BM2" t="n">
         <v>1767139200</v>
@@ -4528,19 +4747,19 @@
         <v>-782899968</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-1.86</v>
+        <v>-2.62</v>
       </c>
       <c r="BR2" t="n">
-        <v>1</v>
+        <v>1.003</v>
       </c>
       <c r="BS2" t="n">
-        <v>46.131</v>
+        <v>46.258</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.58630824</v>
+        <v>0.75945175</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
@@ -4548,7 +4767,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>38.22</v>
+        <v>36.76</v>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
@@ -4647,149 +4866,149 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CY2" t="n">
-        <v>15.457602</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>0.6790849</v>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="DA2" t="n">
-        <v>16.026802</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>0.72214925</v>
-      </c>
-      <c r="DC2" t="n">
+        <v>1781875437</v>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>finmb_140687018</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Europe/Rome</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>it_market</t>
+        </is>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>Delivery Hero SE</t>
+        </is>
+      </c>
+      <c r="DJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>1700121600000</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>-0.47000122</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>36.72 - 36.76</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>1193</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1.4425248</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>15.05 - 39.69</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>-2.9300003</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.07382213</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>75.94517500000001</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1774542600</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1774542600</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1774542600</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>1774530000</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1774530000</v>
+      </c>
+      <c r="EA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>DELIVERY HERO</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>8.340598999999999</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0.2934826</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>13.665298</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>0.5917071</v>
+      </c>
+      <c r="EH2" t="n">
         <v>20</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="EI2" t="n">
         <v>15</v>
       </c>
-      <c r="DE2" t="b">
+      <c r="EJ2" t="b">
         <v>0</v>
       </c>
-      <c r="DF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>1700121600000</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>0.45000076</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>38.16 - 38.16</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>Milan</t>
-        </is>
-      </c>
-      <c r="DK2" t="n">
-        <v>1415</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>23.170002</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>1.539535</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>15.05 - 39.1</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.87999725</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.022506325</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>58.630825</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1774542600</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1774542600</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1774542600</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1774530000</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1774530000</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-1.86</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>1780404830</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>finmb_140687018</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>Europe/Rome</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>it_market</t>
-        </is>
-      </c>
-      <c r="EG2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>DELIVERY HERO</t>
-        </is>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>Delivery Hero SE</t>
-        </is>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1.1914238</v>
-      </c>
       <c r="EK2" t="n">
-        <v>38.22</v>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
+        <v>-1.2624261</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>36.76</v>
       </c>
       <c r="EM2" t="inlineStr"/>
     </row>
